--- a/artfynd/A 62868-2020 artfynd.xlsx
+++ b/artfynd/A 62868-2020 artfynd.xlsx
@@ -3926,7 +3926,7 @@
         <v>113178183</v>
       </c>
       <c r="B29" t="n">
-        <v>78140</v>
+        <v>78156</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>113178181</v>
       </c>
       <c r="B30" t="n">
-        <v>77776</v>
+        <v>77792</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>113178182</v>
       </c>
       <c r="B31" t="n">
-        <v>90296</v>
+        <v>90312</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 62868-2020 artfynd.xlsx
+++ b/artfynd/A 62868-2020 artfynd.xlsx
@@ -3923,10 +3923,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113178183</v>
+        <v>113178181</v>
       </c>
       <c r="B29" t="n">
-        <v>78156</v>
+        <v>77792</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3939,21 +3939,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519725</v>
+        <v>519453</v>
       </c>
       <c r="R29" t="n">
-        <v>6939750</v>
+        <v>6939690</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4012,12 +4012,15 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>120-årig gles barrblandskog med större lövinslag</t>
-        </is>
+          <t>120-årig gles tallskog med större lövinslag, viss granunderväxt i blockmark</t>
+        </is>
+      </c>
+      <c r="AN29" t="n">
+        <v>1</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>torra grenar på senvuxen gran</t>
+          <t>1 substratenheter # hängande grov rest av gammal tallåga</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4039,10 +4042,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113178181</v>
+        <v>113178183</v>
       </c>
       <c r="B30" t="n">
-        <v>77792</v>
+        <v>78156</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4055,21 +4058,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4079,10 +4082,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519453</v>
+        <v>519725</v>
       </c>
       <c r="R30" t="n">
-        <v>6939690</v>
+        <v>6939750</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4128,15 +4131,12 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>120-årig gles tallskog med större lövinslag, viss granunderväxt i blockmark</t>
-        </is>
-      </c>
-      <c r="AN30" t="n">
-        <v>1</v>
+          <t>120-årig gles barrblandskog med större lövinslag</t>
+        </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>1 substratenheter # hängande grov rest av gammal tallåga</t>
+          <t>torra grenar på senvuxen gran</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 62868-2020 artfynd.xlsx
+++ b/artfynd/A 62868-2020 artfynd.xlsx
@@ -3926,7 +3926,7 @@
         <v>113178181</v>
       </c>
       <c r="B29" t="n">
-        <v>77792</v>
+        <v>77804</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>113178183</v>
       </c>
       <c r="B30" t="n">
-        <v>78156</v>
+        <v>78168</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>113178182</v>
       </c>
       <c r="B31" t="n">
-        <v>90312</v>
+        <v>90324</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 62868-2020 artfynd.xlsx
+++ b/artfynd/A 62868-2020 artfynd.xlsx
@@ -3923,10 +3923,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113178181</v>
+        <v>113178182</v>
       </c>
       <c r="B29" t="n">
-        <v>77804</v>
+        <v>90346</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3935,25 +3935,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>71</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>1 substratenheter # hängande grov rest av gammal tallåga</t>
+          <t>1 substratenheter # under hängande grov rest av gammal tallåga</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4042,10 +4042,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113178183</v>
+        <v>113178181</v>
       </c>
       <c r="B30" t="n">
-        <v>78168</v>
+        <v>77826</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4058,21 +4058,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4082,10 +4082,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519725</v>
+        <v>519453</v>
       </c>
       <c r="R30" t="n">
-        <v>6939750</v>
+        <v>6939690</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4131,12 +4131,15 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>120-årig gles barrblandskog med större lövinslag</t>
-        </is>
+          <t>120-årig gles tallskog med större lövinslag, viss granunderväxt i blockmark</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>1</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>torra grenar på senvuxen gran</t>
+          <t>1 substratenheter # hängande grov rest av gammal tallåga</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4158,10 +4161,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113178182</v>
+        <v>113178183</v>
       </c>
       <c r="B31" t="n">
-        <v>90324</v>
+        <v>78190</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4170,25 +4173,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>71</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4198,10 +4201,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519453</v>
+        <v>519725</v>
       </c>
       <c r="R31" t="n">
-        <v>6939690</v>
+        <v>6939750</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4247,15 +4250,12 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>120-årig gles tallskog med större lövinslag, viss granunderväxt i blockmark</t>
-        </is>
-      </c>
-      <c r="AN31" t="n">
-        <v>1</v>
+          <t>120-årig gles barrblandskog med större lövinslag</t>
+        </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>1 substratenheter # under hängande grov rest av gammal tallåga</t>
+          <t>torra grenar på senvuxen gran</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>

--- a/artfynd/A 62868-2020 artfynd.xlsx
+++ b/artfynd/A 62868-2020 artfynd.xlsx
@@ -3926,7 +3926,7 @@
         <v>113178182</v>
       </c>
       <c r="B29" t="n">
-        <v>90346</v>
+        <v>90350</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>113178181</v>
       </c>
       <c r="B30" t="n">
-        <v>77826</v>
+        <v>77829</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>113178183</v>
       </c>
       <c r="B31" t="n">
-        <v>78190</v>
+        <v>78193</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 62868-2020 artfynd.xlsx
+++ b/artfynd/A 62868-2020 artfynd.xlsx
@@ -3923,10 +3923,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113178182</v>
+        <v>113178183</v>
       </c>
       <c r="B29" t="n">
-        <v>90350</v>
+        <v>78193</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3935,25 +3935,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>71</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519453</v>
+        <v>519725</v>
       </c>
       <c r="R29" t="n">
-        <v>6939690</v>
+        <v>6939750</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4012,15 +4012,12 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>120-årig gles tallskog med större lövinslag, viss granunderväxt i blockmark</t>
-        </is>
-      </c>
-      <c r="AN29" t="n">
-        <v>1</v>
+          <t>120-årig gles barrblandskog med större lövinslag</t>
+        </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>1 substratenheter # under hängande grov rest av gammal tallåga</t>
+          <t>torra grenar på senvuxen gran</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4161,10 +4158,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113178183</v>
+        <v>113178182</v>
       </c>
       <c r="B31" t="n">
-        <v>78193</v>
+        <v>90350</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4173,25 +4170,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4201,10 +4198,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519725</v>
+        <v>519453</v>
       </c>
       <c r="R31" t="n">
-        <v>6939750</v>
+        <v>6939690</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4250,12 +4247,15 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>120-årig gles barrblandskog med större lövinslag</t>
-        </is>
+          <t>120-årig gles tallskog med större lövinslag, viss granunderväxt i blockmark</t>
+        </is>
+      </c>
+      <c r="AN31" t="n">
+        <v>1</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>torra grenar på senvuxen gran</t>
+          <t>1 substratenheter # under hängande grov rest av gammal tallåga</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>

--- a/artfynd/A 62868-2020 artfynd.xlsx
+++ b/artfynd/A 62868-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
